--- a/excel_bt1.xlsx
+++ b/excel_bt1.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30619"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AB455C2-5A73-40B0-A98D-0514B3F5729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10440"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tổng hợp" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>BẢNG TỔNG HỢP CHI PHÍ TỪ ĐỐI TÁC NGÂN HÀNG (THÁNG 05/2024)</t>
   </si>
   <si>
-    <t>Column1</t>
+    <t>STT</t>
   </si>
   <si>
     <t>Tên người dùng</t>
@@ -138,9 +142,6 @@
   </si>
   <si>
     <t>SHB</t>
-  </si>
-  <si>
-    <t>STT</t>
   </si>
   <si>
     <t>Mã người dùng</t>
@@ -179,14 +180,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,159 +221,8 @@
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,194 +241,8 @@
         <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -607,251 +265,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -880,61 +296,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1219,14 +591,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
@@ -1238,7 +610,7 @@
     <col min="10" max="10" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" spans="1:10">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +679,7 @@
         <v>1000</v>
       </c>
       <c r="H3" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I3" s="6">
         <f t="shared" ref="I3:I12" si="0">F3*H3</f>
@@ -1341,7 +713,7 @@
         <v>1000</v>
       </c>
       <c r="H4" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I4" s="6">
         <f t="shared" si="0"/>
@@ -1375,7 +747,7 @@
         <v>1000</v>
       </c>
       <c r="H5" s="7">
-        <v>0.0007</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="I5" s="6">
         <f t="shared" si="0"/>
@@ -1409,7 +781,7 @@
         <v>1000</v>
       </c>
       <c r="H6" s="7">
-        <v>0.0007</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="I6" s="6">
         <f t="shared" si="0"/>
@@ -1443,7 +815,7 @@
         <v>1000</v>
       </c>
       <c r="H7" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I7" s="6">
         <f t="shared" si="0"/>
@@ -1477,7 +849,7 @@
         <v>1000</v>
       </c>
       <c r="H8" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I8" s="6">
         <f t="shared" si="0"/>
@@ -1511,7 +883,7 @@
         <v>1000</v>
       </c>
       <c r="H9" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I9" s="6">
         <f t="shared" si="0"/>
@@ -1545,7 +917,7 @@
         <v>1000</v>
       </c>
       <c r="H10" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I10" s="6">
         <f t="shared" si="0"/>
@@ -1579,7 +951,7 @@
         <v>1000</v>
       </c>
       <c r="H11" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I11" s="6">
         <f t="shared" si="0"/>
@@ -1613,7 +985,7 @@
         <v>1000</v>
       </c>
       <c r="H12" s="7">
-        <v>0.0008</v>
+        <v>8.0000000000000004E-4</v>
       </c>
       <c r="I12" s="6">
         <f t="shared" si="0"/>
@@ -1626,13 +998,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="8" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>2</v>
@@ -1649,7 +1021,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>11</v>
@@ -1667,7 +1039,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>14</v>
@@ -1685,7 +1057,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>16</v>
@@ -1703,7 +1075,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>19</v>
@@ -1721,7 +1093,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>22</v>
@@ -1739,7 +1111,7 @@
         <v>26</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>25</v>
@@ -1757,7 +1129,7 @@
         <v>28</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>27</v>
@@ -1775,7 +1147,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>30</v>
@@ -1793,7 +1165,7 @@
         <v>34</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>33</v>
@@ -1811,7 +1183,7 @@
         <v>36</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>35</v>
@@ -1823,6 +1195,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>